--- a/campus_flow_template.xlsx
+++ b/campus_flow_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abe7ae0bb903584c/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85A0A806-4576-4BD5-808C-5925324D70D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{85A0A806-4576-4BD5-808C-5925324D70D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E012979-5B5E-4786-8904-36FA8F1D61A4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="schedule" sheetId="4" r:id="rId4"/>
     <sheet name="attendance" sheetId="5" r:id="rId5"/>
     <sheet name="logs" sheetId="6" r:id="rId6"/>
+    <sheet name="users" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="115">
   <si>
     <t>student_id</t>
   </si>
@@ -322,13 +323,61 @@
   </si>
   <si>
     <t>deepak@gmail.com</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>admin123</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Faculty</t>
+  </si>
+  <si>
+    <t>teach123</t>
+  </si>
+  <si>
+    <t>F101</t>
+  </si>
+  <si>
+    <t>F102</t>
+  </si>
+  <si>
+    <t>F103</t>
+  </si>
+  <si>
+    <t>F104</t>
+  </si>
+  <si>
+    <t>F105</t>
+  </si>
+  <si>
+    <t>stud123</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>sudent_id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,6 +406,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -379,7 +434,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -409,6 +464,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1870,4 +1926,253 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{301039C6-0E68-4E04-B876-BF76D673AFB5}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>102</v>
+      </c>
+      <c r="B9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>103</v>
+      </c>
+      <c r="B10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>104</v>
+      </c>
+      <c r="B11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>105</v>
+      </c>
+      <c r="B12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>107</v>
+      </c>
+      <c r="B14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>108</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>109</v>
+      </c>
+      <c r="B16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>110</v>
+      </c>
+      <c r="B17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/campus_flow_template.xlsx
+++ b/campus_flow_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abe7ae0bb903584c/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{85A0A806-4576-4BD5-808C-5925324D70D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E012979-5B5E-4786-8904-36FA8F1D61A4}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{85A0A806-4576-4BD5-808C-5925324D70D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBD73444-E235-4F77-A6D0-0CC0CA148ECE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="114">
   <si>
     <t>student_id</t>
   </si>
@@ -368,9 +368,6 @@
   </si>
   <si>
     <t>Student</t>
-  </si>
-  <si>
-    <t>sudent_id</t>
   </si>
 </sst>
 </file>
@@ -1932,6 +1929,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{301039C6-0E68-4E04-B876-BF76D673AFB5}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="11.5546875" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
@@ -1944,7 +1945,7 @@
         <v>101</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>10</v>

--- a/campus_flow_template.xlsx
+++ b/campus_flow_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abe7ae0bb903584c/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{85A0A806-4576-4BD5-808C-5925324D70D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBD73444-E235-4F77-A6D0-0CC0CA148ECE}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{85A0A806-4576-4BD5-808C-5925324D70D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{137A3D98-8031-40F0-82DB-12DBFDBFFE49}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,14 @@
     <sheet name="attendance" sheetId="5" r:id="rId5"/>
     <sheet name="logs" sheetId="6" r:id="rId6"/>
     <sheet name="users" sheetId="8" r:id="rId7"/>
+    <sheet name="results" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="117">
   <si>
     <t>student_id</t>
   </si>
@@ -368,6 +369,15 @@
   </si>
   <si>
     <t>Student</t>
+  </si>
+  <si>
+    <t>marks</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>A+</t>
   </si>
 </sst>
 </file>
@@ -2176,4 +2186,241 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F99E3E43-08DD-4F6D-9B92-4D716E0E2668}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>101</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="3">
+        <v>85</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>101</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="3">
+        <v>78</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>101</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3">
+        <v>65</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>102</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="3">
+        <v>92</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>102</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="3">
+        <v>88</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>102</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="3">
+        <v>70</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>103</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="3">
+        <v>45</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>103</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="3">
+        <v>55</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>103</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="3">
+        <v>60</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>104</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="3">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>104</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="3">
+        <v>40</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>104</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="3">
+        <v>50</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>105</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="3">
+        <v>95</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>105</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="3">
+        <v>90</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>105</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="3">
+        <v>85</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/campus_flow_template.xlsx
+++ b/campus_flow_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abe7ae0bb903584c/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{85A0A806-4576-4BD5-808C-5925324D70D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{137A3D98-8031-40F0-82DB-12DBFDBFFE49}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{85A0A806-4576-4BD5-808C-5925324D70D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A69471AA-45F3-4005-B790-D30C88146414}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="112">
   <si>
     <t>student_id</t>
   </si>
@@ -348,21 +348,6 @@
   </si>
   <si>
     <t>teach123</t>
-  </si>
-  <si>
-    <t>F101</t>
-  </si>
-  <si>
-    <t>F102</t>
-  </si>
-  <si>
-    <t>F103</t>
-  </si>
-  <si>
-    <t>F104</t>
-  </si>
-  <si>
-    <t>F105</t>
   </si>
   <si>
     <t>stud123</t>
@@ -1974,7 +1959,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
         <v>106</v>
@@ -1983,12 +1968,12 @@
         <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>106</v>
@@ -1997,12 +1982,12 @@
         <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
         <v>106</v>
@@ -2011,12 +1996,12 @@
         <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
         <v>106</v>
@@ -2025,12 +2010,12 @@
         <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
         <v>106</v>
@@ -2039,7 +2024,7 @@
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2047,10 +2032,10 @@
         <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D8">
         <v>101</v>
@@ -2061,10 +2046,10 @@
         <v>102</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D9">
         <v>102</v>
@@ -2075,10 +2060,10 @@
         <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D10">
         <v>103</v>
@@ -2089,10 +2074,10 @@
         <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D11">
         <v>104</v>
@@ -2103,10 +2088,10 @@
         <v>105</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D12">
         <v>105</v>
@@ -2117,10 +2102,10 @@
         <v>106</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D13">
         <v>106</v>
@@ -2131,10 +2116,10 @@
         <v>107</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D14">
         <v>107</v>
@@ -2145,10 +2130,10 @@
         <v>108</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D15">
         <v>108</v>
@@ -2159,10 +2144,10 @@
         <v>109</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D16">
         <v>109</v>
@@ -2173,10 +2158,10 @@
         <v>110</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D17">
         <v>110</v>
@@ -2204,10 +2189,10 @@
         <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -2263,7 +2248,7 @@
         <v>92</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -2389,7 +2374,7 @@
         <v>95</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -2403,7 +2388,7 @@
         <v>90</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
